--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6ABCE2DE-7501-4474-8A8D-AC0852571062}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4390B4D-564C-4148-9F45-298C31EDCA4E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79E46B29-E226-46AD-A998-D7E4D61C6699}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FE42343-AD8A-477C-B0D1-DB3D49DF18E5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05F294F6-7898-41D4-8D1C-9F8C78468A7E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDFCD56C-BD67-4F2E-A73C-32026F90610F}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4390B4D-564C-4148-9F45-298C31EDCA4E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AE72B74-AAA9-408C-8A17-E55ED80E28F5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FE42343-AD8A-477C-B0D1-DB3D49DF18E5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87652CE0-073C-4E2D-B873-5C22A3470A7F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDFCD56C-BD67-4F2E-A73C-32026F90610F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F960B1CE-CAF0-4E0B-AD95-AC0EEBB0C1D6}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AE72B74-AAA9-408C-8A17-E55ED80E28F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D40513A-48DC-4E67-B4EF-D0E60F099E94}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87652CE0-073C-4E2D-B873-5C22A3470A7F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8653C54-08A7-4410-8049-B0F42845F5F5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F960B1CE-CAF0-4E0B-AD95-AC0EEBB0C1D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6890AEF-FE2D-45A9-B49A-0A0EFA6A512C}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4390B4D-564C-4148-9F45-298C31EDCA4E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02FA3538-8EAB-4C9C-A037-3F27951B2105}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FE42343-AD8A-477C-B0D1-DB3D49DF18E5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF6453D9-0F44-4BBC-BC1E-A6A2984C8B89}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDFCD56C-BD67-4F2E-A73C-32026F90610F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93D80613-DBC6-4561-B955-32C4EA77AAD4}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D40513A-48DC-4E67-B4EF-D0E60F099E94}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35BC0A8E-BF37-450D-B2C7-71BE0A4967FA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8653C54-08A7-4410-8049-B0F42845F5F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55795326-7624-47BC-8BAE-6DCFA9ACEDD9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6890AEF-FE2D-45A9-B49A-0A0EFA6A512C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB3915D-726B-4E3E-9B33-7A7BFC2645C9}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35BC0A8E-BF37-450D-B2C7-71BE0A4967FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D108A5CC-9950-441B-9945-31389EE65561}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55795326-7624-47BC-8BAE-6DCFA9ACEDD9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F80B8A9-841C-44C0-ABE7-5CFC2CEF5D64}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FB3915D-726B-4E3E-9B33-7A7BFC2645C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D3A59D9-AA6C-4F4C-BDD2-A642FFB493EC}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D108A5CC-9950-441B-9945-31389EE65561}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D4DF992-3124-4B8C-8B99-35057D1ACF54}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F80B8A9-841C-44C0-ABE7-5CFC2CEF5D64}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{995E2515-3BDF-4930-BC27-A8B3D3214E2F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D3A59D9-AA6C-4F4C-BDD2-A642FFB493EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{092CDA05-36F2-46FD-A587-C62E7F51508A}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D4DF992-3124-4B8C-8B99-35057D1ACF54}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099761D3-9ACF-47BE-BE36-D46B33827C9D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{995E2515-3BDF-4930-BC27-A8B3D3214E2F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F1692EA-E5C9-4B12-8FD3-B55C97578D8B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{092CDA05-36F2-46FD-A587-C62E7F51508A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29244940-1639-448A-818B-E9813BCABC22}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099761D3-9ACF-47BE-BE36-D46B33827C9D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154E038D-41B5-4012-A36C-8F632B02F8DA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F1692EA-E5C9-4B12-8FD3-B55C97578D8B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{526EE4BB-B1EB-4D92-A84F-EDF8C0EF9400}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29244940-1639-448A-818B-E9813BCABC22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6655ACB0-739A-4378-A2DD-A272CE4E2E25}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154E038D-41B5-4012-A36C-8F632B02F8DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D628AE1-446E-4D99-BCCF-12B667FCC5CB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{526EE4BB-B1EB-4D92-A84F-EDF8C0EF9400}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93AFCC88-9124-4C60-A4E6-F6673556817B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6655ACB0-739A-4378-A2DD-A272CE4E2E25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB923546-3C21-4F59-8457-2CDAA52284A0}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D628AE1-446E-4D99-BCCF-12B667FCC5CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB365E35-7A9D-4F0A-9DC8-9BEE8E328705}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93AFCC88-9124-4C60-A4E6-F6673556817B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08A8D2A1-59E6-4B29-A4B8-3C062A704C20}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB923546-3C21-4F59-8457-2CDAA52284A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5642AF0-BA5E-420D-A297-8E129AE7D658}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB365E35-7A9D-4F0A-9DC8-9BEE8E328705}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{264FBA19-0BDA-4736-AFEC-19F9DDC6E236}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08A8D2A1-59E6-4B29-A4B8-3C062A704C20}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48D7B69E-CC21-4E85-A604-2AAEBCA6FA65}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5642AF0-BA5E-420D-A297-8E129AE7D658}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBC0B4A6-5841-49EE-B591-EAE18A7282FF}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{264FBA19-0BDA-4736-AFEC-19F9DDC6E236}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABC02617-5130-46CC-BDA1-E355C7B26CC5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48D7B69E-CC21-4E85-A604-2AAEBCA6FA65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9835756B-B4B0-499A-8FB5-AFD0FD9A1499}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBC0B4A6-5841-49EE-B591-EAE18A7282FF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D42CCD53-288C-4BB1-B7D7-15B8B0A01673}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABC02617-5130-46CC-BDA1-E355C7B26CC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DB9450D-34A5-4BAB-ACC8-571FEA31A0B2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9835756B-B4B0-499A-8FB5-AFD0FD9A1499}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13F24AD1-4456-46CA-B3A8-22F84AAE0B3E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D42CCD53-288C-4BB1-B7D7-15B8B0A01673}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34656E79-C2C2-4E9D-8105-87822A3FE699}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DB9450D-34A5-4BAB-ACC8-571FEA31A0B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A20E1D0-5A17-452A-80CD-DF8EA7A5E416}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13F24AD1-4456-46CA-B3A8-22F84AAE0B3E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD7263B9-2686-4B09-B343-57A6C1DDB647}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34656E79-C2C2-4E9D-8105-87822A3FE699}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE280E90-B0E4-46B4-A3D5-40AAE1CD67FC}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A20E1D0-5A17-452A-80CD-DF8EA7A5E416}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F84F64CA-DCE8-41A5-AA39-FA1C5E8CB1DE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD7263B9-2686-4B09-B343-57A6C1DDB647}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C49BB3A0-1775-40D1-9E2D-6F1954F018FD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE280E90-B0E4-46B4-A3D5-40AAE1CD67FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EED38DCF-F83C-420E-B7BF-9C04DC8AD1B8}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F84F64CA-DCE8-41A5-AA39-FA1C5E8CB1DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB5E11F8-71CE-4363-AD0F-ADAC5E1DC986}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C49BB3A0-1775-40D1-9E2D-6F1954F018FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEE9ED85-D422-48C2-924E-0A1F30EC2E6B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EED38DCF-F83C-420E-B7BF-9C04DC8AD1B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3336A24D-8A77-475D-B1A8-721C8B7FCBCB}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB5E11F8-71CE-4363-AD0F-ADAC5E1DC986}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA42CE0B-2653-439D-BE54-636591F7A9E0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEE9ED85-D422-48C2-924E-0A1F30EC2E6B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F318541D-705D-4B1E-8F8B-64879493D871}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3336A24D-8A77-475D-B1A8-721C8B7FCBCB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E049E769-6777-4095-B48C-188239861DEE}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA42CE0B-2653-439D-BE54-636591F7A9E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19E8AA31-3B0B-4F8A-9FB4-62475BDCDDD9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F318541D-705D-4B1E-8F8B-64879493D871}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB163747-2F61-4B9A-95D7-0287A7407430}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E049E769-6777-4095-B48C-188239861DEE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F05701BD-1CFE-4D84-A781-0132747D5DFA}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19E8AA31-3B0B-4F8A-9FB4-62475BDCDDD9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFCEC1CC-22E1-467A-B7BD-CBDC5080C2BE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB163747-2F61-4B9A-95D7-0287A7407430}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB5652C-634F-4E10-ACEE-1227EA11A40C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F05701BD-1CFE-4D84-A781-0132747D5DFA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD5C562-2FD4-41DC-BD6F-30B54880B5FA}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFCEC1CC-22E1-467A-B7BD-CBDC5080C2BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB1FC9F9-B12C-4B13-AB3B-09112C0D9DCC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB5652C-634F-4E10-ACEE-1227EA11A40C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E72FFAF9-B8E4-44B0-8F22-B0644AB3DAC1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD5C562-2FD4-41DC-BD6F-30B54880B5FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D58B1D5-C463-47A1-8C7A-2A342B411249}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB1FC9F9-B12C-4B13-AB3B-09112C0D9DCC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974FB87A-8FFF-4C0C-BFDD-E315ADEB32BA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E72FFAF9-B8E4-44B0-8F22-B0644AB3DAC1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B34D4405-FCD2-4673-BF29-2155160875C1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D58B1D5-C463-47A1-8C7A-2A342B411249}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A131C97E-3D01-44FE-B72B-3A1D1FAAA7CB}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974FB87A-8FFF-4C0C-BFDD-E315ADEB32BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8D7F05F-2C57-46A2-8EAE-3759FCCFDB90}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B34D4405-FCD2-4673-BF29-2155160875C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{530E03C3-3B03-4D9C-A38A-9FCBD866BB52}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A131C97E-3D01-44FE-B72B-3A1D1FAAA7CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{592EAB3C-2B7B-4515-B36F-37238F23CCB9}"/>
 </file>
--- a/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
+++ b/____EvoM1_TraitTable/interlaminar_astrocytes.xlsx
@@ -4079,13 +4079,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8D7F05F-2C57-46A2-8EAE-3759FCCFDB90}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EEF7463-274A-4A85-9126-16DB61FBF1A9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{530E03C3-3B03-4D9C-A38A-9FCBD866BB52}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B872F2AF-932F-4ABC-AD67-FFED45E70AC5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{592EAB3C-2B7B-4515-B36F-37238F23CCB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{860AC6EA-37F7-43BA-92EA-2E80523E3F54}"/>
 </file>